--- a/documentation/evaluation_dataset.xlsx
+++ b/documentation/evaluation_dataset.xlsx
@@ -8,12 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dani\Desktop\MASTER\TFM\tfm\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DF55F0B-A46D-4E4D-B699-042A355D9B80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{790AEA35-6513-4635-8AEC-5F3C7B44BC6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D9935ECE-2941-4433-987F-B570949C2821}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{D9935ECE-2941-4433-987F-B570949C2821}"/>
   </bookViews>
   <sheets>
-    <sheet name="A2" sheetId="2" r:id="rId1"/>
+    <sheet name="A1" sheetId="7" r:id="rId1"/>
+    <sheet name="A2" sheetId="2" r:id="rId2"/>
+    <sheet name="C1" sheetId="3" r:id="rId3"/>
+    <sheet name="C2" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="580">
   <si>
     <t>id</t>
   </si>
@@ -190,9 +193,6 @@
     <t>Cualquier conducta realizada por razón de alguna de las causas de discriminación previstas en esta ley, con el objetivo o la consecuencia de atentar contra la dignidad de una persona o grupo en que se integra y de crear un entorno intimidatorio, hostil, degradante, humillante u ofensivo</t>
   </si>
   <si>
-    <t>doc236</t>
-  </si>
-  <si>
     <t>Artículo 3.</t>
   </si>
   <si>
@@ -479,27 +479,6 @@
     <t>Artículo 70.</t>
   </si>
   <si>
-    <t>¿Es posible nombrar a una Subdirectora General en la Administración General del Estado mediante adscripción provisional?</t>
-  </si>
-  <si>
-    <t>No, los puestos de personal directivo público profesional no pueden cubrirse de manera provisional.</t>
-  </si>
-  <si>
-    <t>Artículo 127.</t>
-  </si>
-  <si>
-    <t>doc172</t>
-  </si>
-  <si>
-    <t>¿Cómo se denominan los instrumentos de planificación de carácter abierto y permanente, en los que se podrán incluir puestos de trabajo vacantes, para fomentar una mayor ocupación de las plazas de necesaria cobertura y favorecer una movilidad ordenada y coordinada?</t>
-  </si>
-  <si>
-    <t>Concursos unitarios.</t>
-  </si>
-  <si>
-    <t>Artículo 111.</t>
-  </si>
-  <si>
     <t>¿Cuál de las siguientes afirmaciones sobre los trienios es correcta?
 a) Serán iguales, en todas las Administraciones públicas, para cada uno de los grupos de clasificación según el nivel del complemento de destino que se perciba.
 b) Corresponde al índice de proporcionalidad asignado anualmente a cada uno de los grupos en que se organizan los Cuerpos y Escalas, Clases o Categorías.
@@ -814,6 +793,1156 @@
   </si>
   <si>
     <t>A2_055</t>
+  </si>
+  <si>
+    <t>¿Es compatible el desempeño de un puesto de funcionario de carrera de la Administración General del Estado con el de cargo electivo, miembro de una corporación local?</t>
+  </si>
+  <si>
+    <t>Sí, salvo que en la corporación local desempeñe cargos retribuidos en régimen de dedicación exclusiva.</t>
+  </si>
+  <si>
+    <t>Artículo quinto.</t>
+  </si>
+  <si>
+    <t>doc054</t>
+  </si>
+  <si>
+    <t>¿Qué nivel de especificación tienen las inversiones reales en el presupuesto del Estado?</t>
+  </si>
+  <si>
+    <t>Artículo 43.</t>
+  </si>
+  <si>
+    <t>Capítulo.</t>
+  </si>
+  <si>
+    <t>C1_001</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>C1_002</t>
+  </si>
+  <si>
+    <t>C1_003</t>
+  </si>
+  <si>
+    <t>C1_004</t>
+  </si>
+  <si>
+    <t>C1_005</t>
+  </si>
+  <si>
+    <t>C1_006</t>
+  </si>
+  <si>
+    <t>C1_007</t>
+  </si>
+  <si>
+    <t>C1_008</t>
+  </si>
+  <si>
+    <t>C1_009</t>
+  </si>
+  <si>
+    <t>C1_010</t>
+  </si>
+  <si>
+    <t>C1_011</t>
+  </si>
+  <si>
+    <t>C1_012</t>
+  </si>
+  <si>
+    <t>C1_013</t>
+  </si>
+  <si>
+    <t>C1_014</t>
+  </si>
+  <si>
+    <t>C1_015</t>
+  </si>
+  <si>
+    <t>C1_016</t>
+  </si>
+  <si>
+    <t>C1_017</t>
+  </si>
+  <si>
+    <t>C1_018</t>
+  </si>
+  <si>
+    <t>C1_019</t>
+  </si>
+  <si>
+    <t>C1_020</t>
+  </si>
+  <si>
+    <t>C1_021</t>
+  </si>
+  <si>
+    <t>C1_022</t>
+  </si>
+  <si>
+    <t>C1_023</t>
+  </si>
+  <si>
+    <t>C1_024</t>
+  </si>
+  <si>
+    <t>C1_025</t>
+  </si>
+  <si>
+    <t>C1_026</t>
+  </si>
+  <si>
+    <t>C1_027</t>
+  </si>
+  <si>
+    <t>C1_028</t>
+  </si>
+  <si>
+    <t>C1_029</t>
+  </si>
+  <si>
+    <t>C1_030</t>
+  </si>
+  <si>
+    <t>C1_031</t>
+  </si>
+  <si>
+    <t>C1_032</t>
+  </si>
+  <si>
+    <t>C1_033</t>
+  </si>
+  <si>
+    <t>C1_034</t>
+  </si>
+  <si>
+    <t>C1_035</t>
+  </si>
+  <si>
+    <t>C1_036</t>
+  </si>
+  <si>
+    <t>C1_037</t>
+  </si>
+  <si>
+    <t>C1_038</t>
+  </si>
+  <si>
+    <t>C1_039</t>
+  </si>
+  <si>
+    <t>C1_040</t>
+  </si>
+  <si>
+    <t>C1_041</t>
+  </si>
+  <si>
+    <t>C1_042</t>
+  </si>
+  <si>
+    <t>C1_043</t>
+  </si>
+  <si>
+    <t>C1_044</t>
+  </si>
+  <si>
+    <t>C1_045</t>
+  </si>
+  <si>
+    <t>C1_046</t>
+  </si>
+  <si>
+    <t>C1_047</t>
+  </si>
+  <si>
+    <t>C1_048</t>
+  </si>
+  <si>
+    <t>C1_049</t>
+  </si>
+  <si>
+    <t>C1_050</t>
+  </si>
+  <si>
+    <t>C1_051</t>
+  </si>
+  <si>
+    <t>C1_052</t>
+  </si>
+  <si>
+    <t>C1_053</t>
+  </si>
+  <si>
+    <t>C1_054</t>
+  </si>
+  <si>
+    <t>C1_055</t>
+  </si>
+  <si>
+    <t>¿Cómo deberan ser aprobados los proyectos de reforma constitucional?</t>
+  </si>
+  <si>
+    <t>Por mayoría de tres quintos de cada una de las Cámaras.</t>
+  </si>
+  <si>
+    <t>Artículo 167.</t>
+  </si>
+  <si>
+    <t>¿Quién nombrará al Presidente del Tribunal Supremo de acuerdo con lo previsto en el artículo 123 de la Constitución Española de 1978?</t>
+  </si>
+  <si>
+    <t>El Rey, a propuesta del Consejo del Poder Judicial, en la forma que determine la ley.</t>
+  </si>
+  <si>
+    <t>Artículo 123.</t>
+  </si>
+  <si>
+    <t>El derecho de acceso a la información pública podrá ser limitado cuando acceder a la información suponga un perjuicio para:
+a) La seguridad nacional.
+b) La seguridad e higiene en el trabajo.
+c) La protección del anonimato de los empleados públicos.
+d) La protección de datos de carácter profesional.</t>
+  </si>
+  <si>
+    <t>La seguridad nacional.</t>
+  </si>
+  <si>
+    <t>Artículo 14.</t>
+  </si>
+  <si>
+    <t>¿A qué municipios se les aplicará el régimen de organización de los municipios de gran población?</t>
+  </si>
+  <si>
+    <t>A los municipios que sean capitales de provincia, capitales autonómicas o sedes de las instituciones autonómicas cuando así lo decidan las Asambleas Legislativas correspondientes a iniciativa de los respectivos ayuntamientos.</t>
+  </si>
+  <si>
+    <t>Artículo 121.</t>
+  </si>
+  <si>
+    <t>Señale la respuesta correcta en materia de registros:
+a) Los Organismos públicos vinculados o dependientes de cada Administración deberán disponer de su propio registro electrónico plenamente interoperable e interconectado con el Registro Electrónico General de la Administración de la que depende.
+b) Cada Administración dispondrá de un Registro Electrónico General donde se deberá anotar la salida de los documentos oficiales provenientes de otros órganos o particulares.
+c) Las disposiciones de creación de registros electrónicos especificarán el órgano o unidad responsable de su gestión, así como la fecha y hora oficial y los días declarados como hábiles.
+d) Los Organismos públicos vinculados o dependientes de cada Administración podrán disponer de su propio registro electrónico plenamente interoperable e interconectado con el Registro Electrónico General de la Administración de la que depende.</t>
+  </si>
+  <si>
+    <t>Artículo 16.</t>
+  </si>
+  <si>
+    <t>Los Organismos públicos vinculados o dependientes de cada Administración podrán disponer de su propio registro electrónico plenamente interoperable e interconectado con el Registro Electrónico General de la Administración de la que depende.</t>
+  </si>
+  <si>
+    <t>Las Administraciones Públicas, en relación con sus sistemas de identificación:
+a) Podrán hacer pública la relación de certificados electrónicos utilizados, incluyendo las características de los sellos electrónicos y los prestadores que los expiden.
+b) Podrán identificarse mediante el uso de un certificado electrónico reconocido o cualificado.
+c) Deberán identificarse mediante el uso de un sello electrónico basado en una firma electrónica reconocida o cualificada que reúna los requisitos exigidos por la legislación de certificado electrónico.
+d) Podrán identificarse mediante el uso de un sello electrónico basado en un certificado electrónico reconocido o cualificado que reúna los requisitos exigidos por la legislación de firma electrónica.</t>
+  </si>
+  <si>
+    <t>Podrán identificarse mediante el uso de un sello electrónico basado en un certificado electrónico reconocido o cualificado que reúna los requisitos exigidos por la legislación de firma electrónica.</t>
+  </si>
+  <si>
+    <t>Artículo 40.</t>
+  </si>
+  <si>
+    <t>Conforme al artículo 5 de la Ley Orgánica 3/2018, de 5 de diciembre, de Protección de Datos Personales y garantía de los derechos digitales, ¿quiénes están sujetos al deber de confidencialidad?</t>
+  </si>
+  <si>
+    <t>Los responsables y encargados del tratamiento de datos, así como todas las personas que intervengan en cualquier fase de este.</t>
+  </si>
+  <si>
+    <t>Artículo 5.</t>
+  </si>
+  <si>
+    <t>Antes de dictar resolución, el órgano competente para resolver podrá decidir, mediante acuerdo motivado, la realización de actuaciones complementarias indispensables para resolver el procedimiento. ¿En qué plazo se deberán practicar dichas actuaciones complementarias?</t>
+  </si>
+  <si>
+    <t>No superior a quince días.</t>
+  </si>
+  <si>
+    <t>Artículo 87.</t>
+  </si>
+  <si>
+    <t>En relación con la revisión de precios en los contratos celebrados con precios provisionales:
+a) Podrá admitirse la revisión de precios siempre que el período de recuperación de la inversión sea inferior a cinco años.
+b) Podrá admitirse la revisión de precios siempre que el período de recuperación de la inversión sea igual o superior a cinco años.
+c) Podrá admitirse la revisión de precios cuando el contrato se hubiese ejecutado, al menos, en el 20 por ciento de su importe y hubiese transcurrido un año desde su formalización.
+d) No cabrá la revisión de precios.</t>
+  </si>
+  <si>
+    <t>No cabrá la revisión de precios.</t>
+  </si>
+  <si>
+    <t>Artículo 102.</t>
+  </si>
+  <si>
+    <t>¿A quién le corresponde fijar el importe de las indemnizaciones que proceda abonar cuando el Tribunal Constitucional haya declarado, a instancia de parte interesada, la existencia de un funcionamiento anormal en la tramitación de los recursos de amparo o de las cuestiones de inconstitucionalidad?</t>
+  </si>
+  <si>
+    <t>Al Consejo de Ministros.</t>
+  </si>
+  <si>
+    <t>La condición de funcionario de carrera se adquiere, además de por la superación del proceso selectivo, por el cumplimiento del siguiente requisito:
+a) No se exige ningún requisito adicional.
+b) Superar un reconocimiento médico que excluya padecer una enfermedad infectocontagiosa.
+c) Presentar el certificado de penales.
+d) La toma de posesión dentro del plazo señalado.</t>
+  </si>
+  <si>
+    <t>La toma de posesión dentro del plazo señalado.</t>
+  </si>
+  <si>
+    <t>doc195</t>
+  </si>
+  <si>
+    <t>Los funcionarios de carrera se hallan en situación de servicio activo:
+a) Cuando acceden a la condición de Diputado o Senador.
+b) Cuando se encuentren en comisión de servicios.
+c) Cuando sean transferidos a una comunidad autónoma.
+d) Cuando estén en expectativa de destino</t>
+  </si>
+  <si>
+    <t>Cuando se encuentren en comisión de servicios</t>
+  </si>
+  <si>
+    <t>De acuerdo con el artículo 5 del Real Decreto Legislativo 4/2000, de 23 de junio, por el que se aprueba el texto refundido de la Ley sobre Seguridad Social de los Funcionarios Civiles del Estado, ¿cómo se integra en el Sector Público Institucional Estatal la Mutualidad General de Funcionarios Civiles del Estado (MUFACE)?</t>
+  </si>
+  <si>
+    <t>Como organismo público.</t>
+  </si>
+  <si>
+    <t>En el supuesto de jubilación parcial del personal laboral sujeto al IV Convenio único que tenga reconocida una discapacidad en grado igual o superior al 33 por ciento, ¿qué período de cotización mínimo se deberá acreditar para acceder a la prestación?</t>
+  </si>
+  <si>
+    <t>Veinticinco años.</t>
+  </si>
+  <si>
+    <t>Artículo 215.</t>
+  </si>
+  <si>
+    <t>Señale la respuesta correcta en relación con el proyecto de Ley de los Presupuestos Generales del Estado:
+a) El Gobierno deberá presentar ante el Congreso de los Diputados los Presupuestos Generales del Estado al menos seis meses antes de la expiración de los del año anterior.
+b) Corresponderá al Ministro de la Presidencia elevar al acuerdo del Gobierno el anteproyecto de la Ley de Presupuestos Generales del Estado.
+c) Será remitido a las Cortes Generales antes del día 1 de octubre del año anterior al que se refiera.
+d) Corresponderá al Ministro de Hacienda aprobar el anteproyecto de la Ley de Presupuestos Generales del Estado</t>
+  </si>
+  <si>
+    <t>Será remitido a las Cortes Generales antes del día 1 de octubre del año anterior al que se refiera.</t>
+  </si>
+  <si>
+    <t>Artículo 37.</t>
+  </si>
+  <si>
+    <t>De conformidad con el artículo 58 de la Ley 47/2003, de 26 de noviembre, General Presupuestaria, ¿mediante qué se financiarán las incorporaciones de crédito que afecten al presupuesto del Estado?</t>
+  </si>
+  <si>
+    <t>Baja en el Fondo de Contingencia o baja en otros créditos de operaciones no financieras.</t>
+  </si>
+  <si>
+    <t>Artículo 58.</t>
+  </si>
+  <si>
+    <t>¿Cuál de las siguientes funciones le corresponde al Tribunal de Cuentas?
+a) El control financiero permanente.
+b) La fiscalización externa, permanente y consuntiva de la actividad económico-financiera del sector público.
+c) La función interventor</t>
+  </si>
+  <si>
+    <t>La fiscalización externa, permanente y consuntiva de la actividad económico-financiera del sector público.</t>
+  </si>
+  <si>
+    <t>Artículo 2.</t>
+  </si>
+  <si>
+    <t>doc129</t>
+  </si>
+  <si>
+    <t>doc166</t>
+  </si>
+  <si>
+    <t>¿Cuándo deberán justificar los Cajeros pagadores la aplicación de las cantidades recibidas?</t>
+  </si>
+  <si>
+    <t>Dentro del mes siguiente a la inversión de las mismas y en todo caso en el plazo de tres meses desde la percepción de los correspondientes fondos</t>
+  </si>
+  <si>
+    <t>¿Quién tiene la competencia para la concesión de una subvención de cuantía de 10 millones de euros en un Organismo Autónomo?</t>
+  </si>
+  <si>
+    <t>El Presidente o Director del Organismo Autónomo; esta competencia podrá ser objeto de desconcentración</t>
+  </si>
+  <si>
+    <t>¿Qué Comisión se designará en las Cortes Generales para relacionarse con el Defensor del Pueblo e informar a los respectivos Plenos en cuantas ocasiones sea necesario?</t>
+  </si>
+  <si>
+    <t>¿Podrá la Comisión General de Secretarios de Estado y Subsecretarios adoptar decisiones o acuerdos por delegación del Gobierno?</t>
+  </si>
+  <si>
+    <t>Una Comisión Mixta Congreso-Senado</t>
+  </si>
+  <si>
+    <t>No, en ningún caso.</t>
+  </si>
+  <si>
+    <t>doc091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuál de las siguientes opciones es correcta respecto a los Estatutos de Autonomía?
+a) Son la norma institucional superior de cada comunidad autónoma y del Estado.
+b) El Estado los reconocerá y amparará como parte integrante de su ordenamiento jurídico.
+c) El procedimiento de reforma requerirá, en todo caso, la celebración de un referéndum y la aprobación por las Cortes Generales, mediante ley orgánica.
+d) Se aprueban por ley ordinaria. </t>
+  </si>
+  <si>
+    <t>El Estado los reconocerá y amparará como parte integrante de su ordenamiento jurídico.</t>
+  </si>
+  <si>
+    <t>Artículo 147.</t>
+  </si>
+  <si>
+    <t>¿Por quién será nombrada la presidencia de la Agencia Española de Protección de Datos?</t>
+  </si>
+  <si>
+    <t>El Gobierno, a propuesta del Ministerio de Justicia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Según el Real Decreto 208/1996, de 9 de febrero, por el que se regulan los servicios de información administrativa y atención al ciudadano, ¿quién ostentará la jefatura de la unidad departamental de información administrativa en cada Ministerio? </t>
+  </si>
+  <si>
+    <t>doc207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El titular de la Subdirección General que tenga encomendada la competencia sobre la información administrativa. </t>
+  </si>
+  <si>
+    <t>Según el artículo 10 del texto refundido de la Ley del Estatuto Básico del Empleado Público, ¿en qué circunstancia se puede nombrar a un funcionario interino?</t>
+  </si>
+  <si>
+    <t>Para la sustitución transitoria de los titulares, durante el tiempo estrictamente necesario.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La modificación de la clasificación profesional de determinados colectivos de personal, sólo podrá ser aprobada:
+a) Por la Subcomisión Paritaria a la que pertenezca.
+b) Por la Comisión Negociadora del Convenio.
+c) Por la Comisión Paritaria.
+d) Por mayoría del colectivo afectado. </t>
+  </si>
+  <si>
+    <t>Por la Comisión Negociadora del Convenio.</t>
+  </si>
+  <si>
+    <t>Artículo 11.</t>
+  </si>
+  <si>
+    <t>Al Director General del Tesoro y Política Financiera.</t>
+  </si>
+  <si>
+    <t>¿A quién le competen las funciones de Ordenador General de pagos del Estado?</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>doc027</t>
+  </si>
+  <si>
+    <t>doc073</t>
+  </si>
+  <si>
+    <t>doc094</t>
+  </si>
+  <si>
+    <t>doc130</t>
+  </si>
+  <si>
+    <t>doc158</t>
+  </si>
+  <si>
+    <t>doc184</t>
+  </si>
+  <si>
+    <t>doc199</t>
+  </si>
+  <si>
+    <t>doc204</t>
+  </si>
+  <si>
+    <t>doc222</t>
+  </si>
+  <si>
+    <t>C2_001</t>
+  </si>
+  <si>
+    <t>C2_002</t>
+  </si>
+  <si>
+    <t>C2_003</t>
+  </si>
+  <si>
+    <t>C2_004</t>
+  </si>
+  <si>
+    <t>C2_005</t>
+  </si>
+  <si>
+    <t>C2_006</t>
+  </si>
+  <si>
+    <t>C2_007</t>
+  </si>
+  <si>
+    <t>C2_008</t>
+  </si>
+  <si>
+    <t>C2_009</t>
+  </si>
+  <si>
+    <t>C2_010</t>
+  </si>
+  <si>
+    <t>C2_011</t>
+  </si>
+  <si>
+    <t>C2_012</t>
+  </si>
+  <si>
+    <t>C2_013</t>
+  </si>
+  <si>
+    <t>C2_014</t>
+  </si>
+  <si>
+    <t>C2_015</t>
+  </si>
+  <si>
+    <t>C2_016</t>
+  </si>
+  <si>
+    <t>C2_017</t>
+  </si>
+  <si>
+    <t>C2_018</t>
+  </si>
+  <si>
+    <t>C2_019</t>
+  </si>
+  <si>
+    <t>C2_020</t>
+  </si>
+  <si>
+    <t>C2_021</t>
+  </si>
+  <si>
+    <t>C2_022</t>
+  </si>
+  <si>
+    <t>C2_023</t>
+  </si>
+  <si>
+    <t>C2_024</t>
+  </si>
+  <si>
+    <t>C2_025</t>
+  </si>
+  <si>
+    <t>C2_026</t>
+  </si>
+  <si>
+    <t>C2_027</t>
+  </si>
+  <si>
+    <t>C2_028</t>
+  </si>
+  <si>
+    <t>C2_029</t>
+  </si>
+  <si>
+    <t>C2_030</t>
+  </si>
+  <si>
+    <t>C2_031</t>
+  </si>
+  <si>
+    <t>C2_032</t>
+  </si>
+  <si>
+    <t>C2_033</t>
+  </si>
+  <si>
+    <t>C2_034</t>
+  </si>
+  <si>
+    <t>C2_035</t>
+  </si>
+  <si>
+    <t>C2_036</t>
+  </si>
+  <si>
+    <t>C2_037</t>
+  </si>
+  <si>
+    <t>C2_038</t>
+  </si>
+  <si>
+    <t>C2_039</t>
+  </si>
+  <si>
+    <t>C2_040</t>
+  </si>
+  <si>
+    <t>C2_041</t>
+  </si>
+  <si>
+    <t>C2_042</t>
+  </si>
+  <si>
+    <t>C2_043</t>
+  </si>
+  <si>
+    <t>C2_044</t>
+  </si>
+  <si>
+    <t>C2_045</t>
+  </si>
+  <si>
+    <t>C2_046</t>
+  </si>
+  <si>
+    <t>C2_047</t>
+  </si>
+  <si>
+    <t>C2_048</t>
+  </si>
+  <si>
+    <t>C2_049</t>
+  </si>
+  <si>
+    <t>C2_050</t>
+  </si>
+  <si>
+    <t>C2_051</t>
+  </si>
+  <si>
+    <t>C2_052</t>
+  </si>
+  <si>
+    <t>C2_053</t>
+  </si>
+  <si>
+    <t>C2_054</t>
+  </si>
+  <si>
+    <t>C2_055</t>
+  </si>
+  <si>
+    <t>A1_001</t>
+  </si>
+  <si>
+    <t>A1_002</t>
+  </si>
+  <si>
+    <t>A1_003</t>
+  </si>
+  <si>
+    <t>A1_004</t>
+  </si>
+  <si>
+    <t>A1_005</t>
+  </si>
+  <si>
+    <t>A1_006</t>
+  </si>
+  <si>
+    <t>A1_007</t>
+  </si>
+  <si>
+    <t>A1_008</t>
+  </si>
+  <si>
+    <t>A1_009</t>
+  </si>
+  <si>
+    <t>A1_010</t>
+  </si>
+  <si>
+    <t>A1_011</t>
+  </si>
+  <si>
+    <t>A1_012</t>
+  </si>
+  <si>
+    <t>A1_013</t>
+  </si>
+  <si>
+    <t>A1_014</t>
+  </si>
+  <si>
+    <t>A1_015</t>
+  </si>
+  <si>
+    <t>A1_016</t>
+  </si>
+  <si>
+    <t>A1_017</t>
+  </si>
+  <si>
+    <t>A1_018</t>
+  </si>
+  <si>
+    <t>A1_019</t>
+  </si>
+  <si>
+    <t>A1_020</t>
+  </si>
+  <si>
+    <t>A1_021</t>
+  </si>
+  <si>
+    <t>A1_022</t>
+  </si>
+  <si>
+    <t>A1_023</t>
+  </si>
+  <si>
+    <t>A1_024</t>
+  </si>
+  <si>
+    <t>A1_025</t>
+  </si>
+  <si>
+    <t>A1_026</t>
+  </si>
+  <si>
+    <t>A1_027</t>
+  </si>
+  <si>
+    <t>A1_028</t>
+  </si>
+  <si>
+    <t>A1_029</t>
+  </si>
+  <si>
+    <t>A1_030</t>
+  </si>
+  <si>
+    <t>A1_031</t>
+  </si>
+  <si>
+    <t>A1_032</t>
+  </si>
+  <si>
+    <t>A1_033</t>
+  </si>
+  <si>
+    <t>A1_034</t>
+  </si>
+  <si>
+    <t>A1_035</t>
+  </si>
+  <si>
+    <t>A1_036</t>
+  </si>
+  <si>
+    <t>A1_037</t>
+  </si>
+  <si>
+    <t>A1_038</t>
+  </si>
+  <si>
+    <t>A1_039</t>
+  </si>
+  <si>
+    <t>A1_040</t>
+  </si>
+  <si>
+    <t>A1_041</t>
+  </si>
+  <si>
+    <t>A1_042</t>
+  </si>
+  <si>
+    <t>A1_043</t>
+  </si>
+  <si>
+    <t>A1_044</t>
+  </si>
+  <si>
+    <t>A1_045</t>
+  </si>
+  <si>
+    <t>A1_046</t>
+  </si>
+  <si>
+    <t>A1_047</t>
+  </si>
+  <si>
+    <t>A1_048</t>
+  </si>
+  <si>
+    <t>A1_049</t>
+  </si>
+  <si>
+    <t>A1_050</t>
+  </si>
+  <si>
+    <t>A1_051</t>
+  </si>
+  <si>
+    <t>A1_052</t>
+  </si>
+  <si>
+    <t>A1_053</t>
+  </si>
+  <si>
+    <t>A1_054</t>
+  </si>
+  <si>
+    <t>A1_055</t>
+  </si>
+  <si>
+    <t>Las Fuerzas Armadas constituidas por el Ejército de Tierra, la Armada y el Ejército del Aire, tienen como misión:
+a) Garantizar la soberanía e independencia de España.
+b) Defender su integridad patrimonial y el ordenamiento constitucional.
+c) Defender su integridad territorial y el ordenamiento democrático.
+d) Garantizar la soberanía e individualidad de España.</t>
+  </si>
+  <si>
+    <t>Garantizar la soberanía e independencia de España.</t>
+  </si>
+  <si>
+    <t>¿Cómo se lleva a cabo el nombramiento de los Secretarios de Estado?</t>
+  </si>
+  <si>
+    <t>Por Real Decreto del Consejo de Ministros, a propuesta del Presidente del Gobierno o del miembro del Gobierno a cuyo Departamento pertenezcan.</t>
+  </si>
+  <si>
+    <t>¿Cómo se pueden recurrir las resoluciones dictadas en materia de acceso a la información pública?</t>
+  </si>
+  <si>
+    <t>Mediante recurso contencioso administrativo</t>
+  </si>
+  <si>
+    <t>Señale, de entre las siguientes funciones, cuál corresponde a los Ministros:
+a) Otorgar premios y recompensas propios del Departamento y proponer las que correspondan según sus normas reguladoras.
+b) Convocar y resolver los concursos de personal funcionario.
+c) Desempeñar la jefatura superior de todo el personal del Departamento.
+d) Convocar y resolver pruebas selectivas de personal funcionario y laboral</t>
+  </si>
+  <si>
+    <t>Otorgar premios y recompensas propios del Departamento y proponer las que correspondan según sus normas reguladoras</t>
+  </si>
+  <si>
+    <t>Artículo 61.</t>
+  </si>
+  <si>
+    <t>Señale cuál de los siguientes servicios deberá prestarse en todos los Municipios:
+a) Pavimentación de las vías públicas.
+b) Tratamiento de residuos.
+c) Prevención y extinción de incendios.
+d) Biblioteca pública.</t>
+  </si>
+  <si>
+    <t>Pavimentación de las vías públicas.</t>
+  </si>
+  <si>
+    <t>Artículo 26.</t>
+  </si>
+  <si>
+    <t>De conformidad con la Ley 39/2015, de 1 de octubre, del Procedimiento Administrativo Común de las Administraciones Públicas, en los procedimientos iniciados a solicitud del interesado, ¿qué consecuencia produciría el vencimiento del plazo máximo sin haberse notificado resolución expresa?</t>
+  </si>
+  <si>
+    <t>Legitimaría al interesado o interesados para entenderla estimada por silencio administrativo, excepto en los supuestos en los que una norma con rango de ley o una norma de Derecho de la Unión Europea o de Derecho internacional aplicable en España establezcan lo contrario.</t>
+  </si>
+  <si>
+    <t>Artículo 24.</t>
+  </si>
+  <si>
+    <t>¿Cuál de las siguientes infracciones está tipificada como muy grave conforme?
+a) La publicación o utilización indebida de la documentación o información a que tengan o hayan tenido acceso por razón de su cargo o función.
+b) El abuso de autoridad en el ejercicio del cargo.
+c) La intervención en un procedimiento administrativo cuando se dé alguna de las causas de abstención legalmente señaladas.
+d) No guardar el debido sigilo respecto a los asuntos que se conozcan por razón del cargo, cuando causen perjuicio a la Administración o se utilice en provecho propio.</t>
+  </si>
+  <si>
+    <t>La publicación o utilización indebida de la documentación o información a que tengan o hayan tenido acceso por razón de su cargo o función.</t>
+  </si>
+  <si>
+    <t>Artículo 29.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ¿En qué situación se encuentran los funcionarios transferidos a las Comunidades Autónomas en la función pública en la que se integran?</t>
+  </si>
+  <si>
+    <t>Servicio activo.</t>
+  </si>
+  <si>
+    <t>Es un principio ético en la actuación de los empleados públicos:
+a) Tratar con atención y respeto a los ciudadanos, a sus superiores y a los restantes empleados públicos.
+b) Administrar los recursos y bienes públicos con austeridad y no utilizar los mismos en provecho propio o de personas allegadas.
+c) No aceptar ningún trato de favor o situación que implique privilegio o ventaja injustificada, por parte de personas físicas o entidades privadas.
+d) Obedecer las instrucciones y órdenes profesionales de los superiores, salvo que constituyan una infracción manifiesta del ordenamiento jurídico, en cuyo caso las pondrán inmediatamente en conocimiento de los órganos de inspección procedentes.</t>
+  </si>
+  <si>
+    <t>No aceptar ningún trato de favor o situación que implique privilegio o ventaja injustificada, por parte de personas físicas o entidades privadas</t>
+  </si>
+  <si>
+    <t>Artículo 53.</t>
+  </si>
+  <si>
+    <t>¿Por quién serán confeccionados  los escenarios presupuestarios plurianuales en los que se enmarcarán anualmente los Presupuestos Generales del Estado?</t>
+  </si>
+  <si>
+    <t>Conforme a la Ley Orgánica 3/2007, de 22 de marzo, para la igualdad efectiva de mujeres y hombres, ¿qué se considera  la situación en que una disposición, criterio o práctica aparentemente neutros pone a personas de un sexo en desventaja particular con respecto a personas del otro, salvo que dicha disposición, criterio o práctica puedan justificarse objetivamente en atención a una finalidad legítima y que los medios para alcanzar dicha finalidad sean necesarios y adecuados?</t>
+  </si>
+  <si>
+    <t>Discriminación indirecta por razón de sexo.</t>
+  </si>
+  <si>
+    <t>Artículo 6.</t>
+  </si>
+  <si>
+    <t>Se considera infracción muy grave:
+a) Los actos discriminatorios u omisiones que supongan directa o indirectamente un trato menos favorable a la persona con discapacidad en relación con otra persona que se encuentre en situación análoga o comparable.
+b) La imposición abusiva de cualquier forma de renuncia total o parcial a los derechos de las personas por motivo de o por razón de su discapacidad, basada en una posición de ventaja.
+c) Las acciones que deliberadamente generen un grave perjuicio económico o profesional para las personas con discapacidad.
+d) La coacción, amenaza, represalia ejercida sobre la persona con discapacidad o sobre otras personas físicas o jurídicas, que hayan entablado o pretendan entablar cualquier clase de acción legal, reclamación, denuncia o participen en procedimientos ya iniciados para exigir el cumplimiento del principio de igualdad de oportunidades, así como la tentativa de ejercitar tales actos.</t>
+  </si>
+  <si>
+    <t>Las acciones que deliberadamente generen un grave perjuicio económico o profesional para las personas con discapacidad.</t>
+  </si>
+  <si>
+    <t>Artículo 95.</t>
+  </si>
+  <si>
+    <t>Según el Real Decreto 208/1996, de 9 de febrero, por el que se regulan los servicios de información administrativa y atención al ciudadano, ¿ de qué formas se clasifica la información administrativa?</t>
+  </si>
+  <si>
+    <t>General y particular.</t>
+  </si>
+  <si>
+    <t>Las cartas de servicios y sus posteriores actualizaciones serán
+aprobadas mediante:
+a) Resolución del Subsecretario del departamento al que pertenezca el órgano y se publicará en el Boletín Oficial del Estado.
+b) Resolución del Subsecretario del departamento al que pertenezca el órgano, no será necesaria la publicación en Boletín Oficial del Estado, pero sí se llevarán a cabo las acciones divulgativas más eficaces, garantizando siempre que puedan ser conocidas por los usuarios en todas sus dependencias con atención al público.
+c) Orden Ministeral del departamento al que pertenezca el órgano y se publicará en el Boletín Oficial del Estado.
+d) Orden Ministerial del departamento al que pertenezca el órgano sin que sea necesaria la publicacion en el Boletín Oficial del Estado, pero se llevarán a cabo las acciones divulgativas más eficaces, garantizando siempre que puedan ser conocidas por los usuarios en todas sus dependencias con atención al público.</t>
+  </si>
+  <si>
+    <t>Resolución del Subsecretario del departamento al que pertenezca el órgano y se publicará en el Boletín Oficial del Estado.</t>
+  </si>
+  <si>
+    <t>¿Cuál es el principio en virtud del cual la sociedad debe permitir que todas las personas con discapacidad tengan las oportunidades y recursos necesarios para participar plenamente en cualquier ámbito de la vida?</t>
+  </si>
+  <si>
+    <t>Inclusión social.</t>
+  </si>
+  <si>
+    <t>¿Qué principio se define como "la capacidad de las Administraciones Públicas para que partiendo del conocimiento adquirido del usuario final del servicio, proporcione servicios precumplimentados y se anticipe a las necesidades"?</t>
+  </si>
+  <si>
+    <t>Personalización y proactividad.</t>
+  </si>
+  <si>
+    <t>¿Quién nombra, conforme a lo previsto en la Constitución Española de 1978, a los miembros del Tribunal Constitucional?</t>
+  </si>
+  <si>
+    <t>El Rey.</t>
+  </si>
+  <si>
+    <t>Artículo 159.</t>
+  </si>
+  <si>
+    <t>¿Cuál de las siguientes facultades podrá ejercer el Presidente del Gobierno en funciones?
+a) Proponer al Rey la convocatoria de un referéndum consultivo.
+b) Plantear la cuestión de confianza.
+c) Proponer al Rey la disolución de alguna de las Cámaras, o de las Cortes Generales.
+d) Aprobar decretos leyes.</t>
+  </si>
+  <si>
+    <t>Aprobar decretos leyes.</t>
+  </si>
+  <si>
+    <t>Artículo 21.</t>
+  </si>
+  <si>
+    <t>Previa su declaración de lesividad para el interés público, las Administraciones Públicas podrán impugnar ante el orden jurisdiccional contencioso-administrativo:
+a) Los actos favorables para los interesados que sean anulables.
+b) Los actos desfavorables para los interesados que sean nulos de pleno derecho.
+c) Los actos favorables y desfavorables para los interesados que sean anulables.
+d) Los actos favorables para los interesados, ya sean nulos de pleno derecho o anulables.</t>
+  </si>
+  <si>
+    <t>Los actos favorables para los interesados que sean anulables.</t>
+  </si>
+  <si>
+    <t>Artículo 107.</t>
+  </si>
+  <si>
+    <t>¿Cuál de las siguientes entidades es un organismo público vinculado o dependiente de la Administración General del Estado?
+a) Sociedades mercantiles.
+b) Autoridades administrativas independientes.
+c) Fondos sin personalidad jurídica.
+d) Entidades Públicas Empresariales.</t>
+  </si>
+  <si>
+    <t>Entidades Públicas Empresariales.</t>
+  </si>
+  <si>
+    <t>¿De qué ministerio depende  el Consejo de Participación de personas LGTBI?</t>
+  </si>
+  <si>
+    <t>Ministerio de Igualdad.</t>
+  </si>
+  <si>
+    <t>¿Mediante qué sistema se realizará la provisión de puestos de personal directivo público profesional en la Administración del Estado?</t>
+  </si>
+  <si>
+    <t>Libre designación.</t>
+  </si>
+  <si>
+    <t>Conforme a la Ley Orgánica 3/2007, de 22 de marzo, para la igualdad efectiva de mujeres y hombres, ¿qué se considera la situación en que una disposición, criterio o práctica aparentemente neutros pone a personas de un sexo en desventaja particular con respecto a personas del otro, salvo que dicha disposición, criterio o práctica puedan justificarse objetivamente en atención a una finalidad legítima y que los medios para alcanzar dicha finalidad sean necesarios y adecuados?</t>
+  </si>
+  <si>
+    <t>¿Cuál de las siguientes facultades podrá ejercer el Presidente del Gobierno en funciones?
+a) Proponer al Rey la convocatoria de un referendum consultivo.
+b) Plantear la cuestión de confianza.
+c) Proponer al Rey la disolución de alguna de las Cámaras, o de las Cortes Generales.
+d) Aprobar decretos leyes.</t>
+  </si>
+  <si>
+    <t>El nombramiento del Defensor del Pueblo será acreditado:
+a) Por el Presidente del Gobierno, con su firma.
+b) Solamente por el Presidente del Senado, con su firma.
+c) Conjuntamente por los Presidentes del Congreso y del Senado con sus firmas.
+d) Por el Rey con su firma.</t>
+  </si>
+  <si>
+    <t>De acuerdo con lo establecido en la Ley Orgánica 2/1979, de 3 de octubre, del Tribunal Constitucional, ¿cuántos miembros deben estar presentes para que el Tribunal en Pleno puede adoptar acuerdos?</t>
+  </si>
+  <si>
+    <t>Al menos, dos tercios de los miembros que en cada momento lo compongan.</t>
+  </si>
+  <si>
+    <t>Artículo catorce.</t>
+  </si>
+  <si>
+    <t>Según lo que se dispone en la Ley Orgánica 3/1980, de 22 de abril, del Consejo de Estado, ¿a propuesta de quién se nombra el Secretario General del Consejo de Estado?</t>
+  </si>
+  <si>
+    <t>A propuesta de la Comisión Permanente del Consejo de Estado.</t>
+  </si>
+  <si>
+    <t>Según lo establecido en la Ley 7/1985, de 2 de abril, Reguladora de las Bases del Régimen Local, ¿la coordinación de la prestación del servicio de recogida y tratamiento de residuos es competencia de la Diputación provincial o entidad equivalente en municipios con qué población?</t>
+  </si>
+  <si>
+    <t>Población inferior a 20.000 habitantes.</t>
+  </si>
+  <si>
+    <t>Según la Ley 42/2007, de 13 de diciembre, del Patrimonio Natural y de la Biodiversidad, ¿qué órgano aprobará las estrategias de conservación de especies amenazadas presentes en más de una comunidad autónoma?</t>
+  </si>
+  <si>
+    <t>La Conferencia Sectorial de Medio Ambiente, a propuesta de la Comisión Estatal para el Patrimonio Natural y la Biodiversidad, y previo informe del Consejo Estatal para el Patrimonio Natural y la Biodiversidad.</t>
+  </si>
+  <si>
+    <t>De acuerdo con el artículo 10 de la Ley 1/2023, de 20 de febrero, de Cooperación para el Desarrollo Sostenible y la Solidaridad Global, ¿cómo puede definirse la cooperación técnica?</t>
+  </si>
+  <si>
+    <t>El conjunto de actividades dirigidas bien al fortalecimiento de capacidades institucionales y de recursos humanos del país socio y de los actores de desarrollo, públicos, privados y de iniciativa social, bien al apoyo de la gestión integral del ciclo de proyectos y programas de cooperación y otras operaciones de cooperación financiera reembolsable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Según la Ley 2/2014, de 25 de marzo, de la Acción y del Servicio Exterior del Estado, ¿cuál es el órgano colegiado de apoyo y asesoramiento al Presidente del Gobierno en el desempeño de su función de dirección y coordinación de la Política Exterior?</t>
+  </si>
+  <si>
+    <t>El Consejo de Política Exterior</t>
+  </si>
+  <si>
+    <t>Artículo 38.</t>
+  </si>
+  <si>
+    <t>El Real Decreto 364/1995, de 10 de marzo, por el que se aprueba el Reglamento General de Ingreso del Personal al servicio de la Administración General del Estado y de Provisión de Puestos de Trabajo y Promoción Profesional de los Funcionarios Civiles de la Administración General del Estado, ¿qué órganos de selección establece en su artículo 10?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Tribunales y las Comisiones Permanentes de Selección. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Según el Real Decreto 365/1995, de 10 de marzo, por el que se aprueba el Reglamento de Situaciones Administrativas de los Funcionarios Civiles de la Administración General del Estado, ¿en qué situación quedará el funcionario declarado en suspensión firme de funciones de no solicitar el reingreso en el tiempo establecido? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">En la situación de excedencia voluntaria por interés particular, con efectos desde la fecha de finalización de la sanción. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Según el artículo 18 de la ley 50/1997, de 27 de noviembre, del Gobierno que regula el funcionamiento del Consejo de Ministros, ¿quién actúa como Secretario de las reuniones de este órgano colegiado? </t>
+  </si>
+  <si>
+    <t>Artículo 18.</t>
+  </si>
+  <si>
+    <t>El Ministro de la Presidencia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En relación con la sucesión en la Corona, extinguidas todas las líneas llamadas en derecho:
+a) El Gobierno proveerá a la sucesión a la Corona en la forma que más convenga a los intereses de los españoles.
+b) Las Cortes Generales proveerán a la sucesión a la Corona en la forma que más convenga a los intereses de España.
+c) El Gobierno proveerá a la sucesión a la Corona en la forma que más convenga a los intereses de España.
+d) El Congreso de los Diputados proveerá a la sucesión a la Corona en la forma que más convenga a los intereses de los españoles. </t>
+  </si>
+  <si>
+    <t>Las Cortes Generales proveerán a la sucesión a la Corona en la forma que más convenga a los intereses de España.</t>
+  </si>
+  <si>
+    <t>Artículo 57.</t>
+  </si>
+  <si>
+    <t>Según el artículo 13 de la Ley 19/2013, de 9 de diciembre, de transparencia, acceso a la información pública y buen gobierno, ¿qué se entiende por los contenidos o documentos, cualquiera que sea su formato o soporte, que obren en poder de alguno de los sujetos incluidos en el ámbito de aplicación de este título y que hayan sido elaborados o adquiridos en el ejercicio de sus funciones?</t>
+  </si>
+  <si>
+    <t>Artículo 13.</t>
+  </si>
+  <si>
+    <t>Información pública.</t>
+  </si>
+  <si>
+    <t>En lo que respecta a los datos sobre las personas físicas fallecidas, señale la opción correcta:
+a) Los familiares no podrán acceder a los datos personales cuando lo prohíba una norma reglamentaria.
+b) Los herederos podrán acceder a los datos de carácter patrimonial del causante en todo caso.
+c) Sólo podrán acceder a los datos personales los familiares hasta el segundo grado de cosanguinidad o afinidad.
+d) Los herederos sólo podrán ejercitar el derecho de cancelación</t>
+  </si>
+  <si>
+    <t>Los herederos podrán acceder a los datos de carácter patrimonial del causante en todo caso.</t>
+  </si>
+  <si>
+    <t>Con carácter general, ¿cual es la duración máxima de una comisión de servicio?</t>
+  </si>
+  <si>
+    <t>No durará más de un mes en territorio nacional y de tres en el extranjero.</t>
+  </si>
+  <si>
+    <t>¿Qué complemento retribuye las condiciones particulares de algunos puestos de trabajo en atención a su especial dificultad técnica, dedicación, responsabilidad, incompatibilidad, peligrosidad o penosidad de un puesto de trabajo?</t>
+  </si>
+  <si>
+    <t>Artículo 23</t>
+  </si>
+  <si>
+    <t>La situación en que se encuentra una persona que sea, haya sido o pudiera ser tratada, en atención a su sexo, de manera menos favorable que otra en situación comparable, se considera:
+a) Acoso sexual.
+b) Acoso por razón de sexo.
+c) Discriminación directa por razón de sexo.
+d) Discriminación indirecta por razón de sexo</t>
+  </si>
+  <si>
+    <t>¿Qué grado corresponde a la situación de dependencia cuando la persona necesita ayuda para realizar varias actividades básicas de la vida diaria, al menos una vez al día o tienen necesidades de apoyo intermitente o limitado para su autonomía personal?</t>
+  </si>
+  <si>
+    <t>Grado I: Dependencia moderada.</t>
   </si>
 </sst>
 </file>
@@ -854,7 +1983,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -877,11 +2006,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -896,6 +2036,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1228,7 +2370,1288 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="438" row="2">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+  <wetp:taskpane dockstate="right" visibility="0" width="438" row="3">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{233845FA-5369-4ABC-9830-66F283016D64}">
+  <we:reference id="wa200009404" version="1.0.0.8" store="es-ES" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="WA200009404" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
+<file path=xl/webextensions/webextension2.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{3765498D-CC9C-4AC3-994A-5CB46F6BD1AA}">
+  <we:reference id="wa200010725" version="1.0.0.1" store="es-ES" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200010725" version="1.0.0.1" store="WA200010725" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;4b509785-1f0c-47bf-9b89-7d450ab702a1&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{209426EC-F1D4-4E4F-A2E8-E9946D929815}">
+  <dimension ref="A1:G56"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="3" max="3" width="14.33203125" customWidth="1"/>
+    <col min="5" max="6" width="19.5546875" customWidth="1"/>
+    <col min="7" max="8" width="18.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ED86784-9DA8-408A-9605-146FD7372791}">
   <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
@@ -1263,7 +3686,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>6</v>
@@ -1286,7 +3709,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>6</v>
@@ -1309,7 +3732,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>6</v>
@@ -1324,15 +3747,15 @@
         <v>43</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>44</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>6</v>
@@ -1341,21 +3764,21 @@
         <v>8</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>6</v>
@@ -1364,21 +3787,21 @@
         <v>8</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="G6" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>6</v>
@@ -1387,21 +3810,21 @@
         <v>8</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>6</v>
@@ -1410,21 +3833,21 @@
         <v>8</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="G8" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>6</v>
@@ -1433,21 +3856,21 @@
         <v>8</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>6</v>
@@ -1456,21 +3879,21 @@
         <v>8</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>33</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>6</v>
@@ -1479,21 +3902,21 @@
         <v>8</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>6</v>
@@ -1502,21 +3925,21 @@
         <v>8</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>6</v>
@@ -1525,21 +3948,21 @@
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>6</v>
@@ -1548,21 +3971,21 @@
         <v>8</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>6</v>
@@ -1571,21 +3994,21 @@
         <v>8</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>6</v>
@@ -1594,21 +4017,21 @@
         <v>8</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>6</v>
@@ -1631,7 +4054,7 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>6</v>
@@ -1640,21 +4063,21 @@
         <v>11</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="F18" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="G18" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>6</v>
@@ -1677,7 +4100,7 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>6</v>
@@ -1686,21 +4109,21 @@
         <v>11</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="F20" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>124</v>
-      </c>
       <c r="G20" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>6</v>
@@ -1709,21 +4132,21 @@
         <v>11</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="F21" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>134</v>
-      </c>
       <c r="G21" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>6</v>
@@ -1732,21 +4155,21 @@
         <v>11</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>135</v>
+        <v>230</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>136</v>
+        <v>231</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>137</v>
+        <v>232</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>138</v>
+        <v>233</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>6</v>
@@ -1755,21 +4178,21 @@
         <v>11</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>139</v>
+        <v>234</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>140</v>
+        <v>236</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>141</v>
+        <v>235</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>138</v>
+        <v>157</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>6</v>
@@ -1778,21 +4201,21 @@
         <v>11</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>6</v>
@@ -1801,21 +4224,21 @@
         <v>11</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>6</v>
@@ -1824,21 +4247,21 @@
         <v>11</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>6</v>
@@ -1847,21 +4270,21 @@
         <v>11</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>6</v>
@@ -1870,21 +4293,21 @@
         <v>11</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>6</v>
@@ -1893,21 +4316,21 @@
         <v>11</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>6</v>
@@ -1916,21 +4339,21 @@
         <v>11</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>6</v>
@@ -1939,21 +4362,21 @@
         <v>11</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>6</v>
@@ -1976,7 +4399,7 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>6</v>
@@ -1999,7 +4422,7 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>6</v>
@@ -2022,7 +4445,7 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>6</v>
@@ -2045,7 +4468,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>6</v>
@@ -2054,21 +4477,21 @@
         <v>9</v>
       </c>
       <c r="D36" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="F36" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G36" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>6</v>
@@ -2077,21 +4500,21 @@
         <v>9</v>
       </c>
       <c r="D37" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F37" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>62</v>
-      </c>
       <c r="G37" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>6</v>
@@ -2100,21 +4523,21 @@
         <v>9</v>
       </c>
       <c r="D38" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E38" t="s">
         <v>64</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="G38" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>6</v>
@@ -2123,21 +4546,21 @@
         <v>9</v>
       </c>
       <c r="D39" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="F39" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="E39" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F39" s="1" t="s">
+      <c r="G39" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>6</v>
@@ -2146,21 +4569,21 @@
         <v>9</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>6</v>
@@ -2169,21 +4592,21 @@
         <v>9</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>6</v>
@@ -2192,21 +4615,21 @@
         <v>9</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>6</v>
@@ -2215,21 +4638,21 @@
         <v>9</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>6</v>
@@ -2238,21 +4661,21 @@
         <v>9</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>6</v>
@@ -2261,13 +4684,13 @@
         <v>9</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>39</v>
@@ -2275,7 +4698,7 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>6</v>
@@ -2284,21 +4707,21 @@
         <v>9</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>6</v>
@@ -2307,7 +4730,7 @@
         <v>10</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
@@ -2315,7 +4738,7 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>6</v>
@@ -2324,7 +4747,7 @@
         <v>10</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
@@ -2332,7 +4755,7 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>6</v>
@@ -2341,7 +4764,7 @@
         <v>10</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
@@ -2349,7 +4772,7 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>6</v>
@@ -2358,7 +4781,7 @@
         <v>10</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
@@ -2366,7 +4789,7 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>6</v>
@@ -2375,7 +4798,7 @@
         <v>10</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
@@ -2383,7 +4806,7 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="4" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>6</v>
@@ -2392,7 +4815,7 @@
         <v>10</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
@@ -2400,7 +4823,7 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="4" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>6</v>
@@ -2409,7 +4832,7 @@
         <v>10</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
@@ -2417,7 +4840,7 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="4" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>6</v>
@@ -2426,7 +4849,7 @@
         <v>10</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
@@ -2434,7 +4857,7 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="4" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>6</v>
@@ -2443,7 +4866,7 @@
         <v>10</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
@@ -2451,7 +4874,7 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="4" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>6</v>
@@ -2460,7 +4883,2493 @@
         <v>10</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>227</v>
+        <v>219</v>
+      </c>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA472574-82D2-4DB1-87C0-4A8A2F9F254D}">
+  <dimension ref="A1:G56"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="3" max="3" width="14.33203125" customWidth="1"/>
+    <col min="5" max="6" width="19.5546875" customWidth="1"/>
+    <col min="7" max="8" width="18.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" t="s">
+        <v>361</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0691D32-4570-4BCC-A08E-9F5A0AFC5038}">
+  <dimension ref="A1:G56"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="3" max="3" width="14.33203125" customWidth="1"/>
+    <col min="5" max="6" width="19.5546875" customWidth="1"/>
+    <col min="7" max="8" width="18.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="E3" t="s">
+        <v>513</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="E27" t="s">
+        <v>574</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>521</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>577</v>
+      </c>
+      <c r="E43" t="s">
+        <v>514</v>
+      </c>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>219</v>
       </c>
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
